--- a/monthly cost.xlsx
+++ b/monthly cost.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46082</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
     </row>
     <row r="5">

--- a/monthly cost.xlsx
+++ b/monthly cost.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46113</v>
+        <v>46143</v>
       </c>
     </row>
     <row r="5">

--- a/monthly cost.xlsx
+++ b/monthly cost.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46143</v>
+        <v>46174</v>
       </c>
     </row>
     <row r="5">

--- a/monthly cost.xlsx
+++ b/monthly cost.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="5">

--- a/monthly cost.xlsx
+++ b/monthly cost.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46204</v>
+        <v>46235</v>
       </c>
     </row>
     <row r="5">

--- a/monthly cost.xlsx
+++ b/monthly cost.xlsx
@@ -463,7 +463,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="4">
@@ -473,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>46235</v>
+        <v>46266</v>
       </c>
     </row>
     <row r="5">
